--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188878</v>
+        <v>113188880</v>
       </c>
       <c r="B2" t="n">
-        <v>90047</v>
+        <v>78121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544229</v>
+        <v>543869</v>
       </c>
       <c r="R2" t="n">
-        <v>7208430</v>
+        <v>7208524</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188892</v>
+        <v>113188891</v>
       </c>
       <c r="B3" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544425</v>
+        <v>544389</v>
       </c>
       <c r="R3" t="n">
-        <v>7208367</v>
+        <v>7208365</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188890</v>
+        <v>113188888</v>
       </c>
       <c r="B4" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544344</v>
+        <v>544228</v>
       </c>
       <c r="R4" t="n">
-        <v>7208412</v>
+        <v>7208430</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188859</v>
+        <v>113188894</v>
       </c>
       <c r="B5" t="n">
-        <v>90029</v>
+        <v>78121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543970</v>
+        <v>544427</v>
       </c>
       <c r="R5" t="n">
-        <v>7208507</v>
+        <v>7208357</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188882</v>
+        <v>113188877</v>
       </c>
       <c r="B6" t="n">
-        <v>78105</v>
+        <v>90063</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543905</v>
+        <v>543877</v>
       </c>
       <c r="R6" t="n">
-        <v>7208555</v>
+        <v>7208540</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188861</v>
+        <v>113188889</v>
       </c>
       <c r="B7" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,39 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544162</v>
+        <v>544243</v>
       </c>
       <c r="R7" t="n">
-        <v>7208445</v>
+        <v>7208437</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,12 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188888</v>
+        <v>113188892</v>
       </c>
       <c r="B8" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544228</v>
+        <v>544425</v>
       </c>
       <c r="R8" t="n">
-        <v>7208430</v>
+        <v>7208367</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188884</v>
+        <v>113188883</v>
       </c>
       <c r="B9" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544013</v>
+        <v>543970</v>
       </c>
       <c r="R9" t="n">
-        <v>7208532</v>
+        <v>7208506</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188880</v>
+        <v>113188876</v>
       </c>
       <c r="B10" t="n">
-        <v>78105</v>
+        <v>90041</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543869</v>
+        <v>544013</v>
       </c>
       <c r="R10" t="n">
-        <v>7208524</v>
+        <v>7208531</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188875</v>
+        <v>113188893</v>
       </c>
       <c r="B11" t="n">
-        <v>78186</v>
+        <v>78121</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544013</v>
+        <v>544429</v>
       </c>
       <c r="R11" t="n">
-        <v>7208532</v>
+        <v>7208373</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188895</v>
+        <v>113188864</v>
       </c>
       <c r="B12" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544444</v>
+        <v>544419</v>
       </c>
       <c r="R12" t="n">
-        <v>7208349</v>
+        <v>7208372</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188886</v>
+        <v>113188865</v>
       </c>
       <c r="B13" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,34 +1928,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544163</v>
+        <v>544430</v>
       </c>
       <c r="R13" t="n">
-        <v>7208441</v>
+        <v>7208372</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188865</v>
+        <v>113188879</v>
       </c>
       <c r="B14" t="n">
-        <v>56765</v>
+        <v>90063</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,39 +2045,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544430</v>
+        <v>544428</v>
       </c>
       <c r="R14" t="n">
-        <v>7208372</v>
+        <v>7208357</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188864</v>
+        <v>113188898</v>
       </c>
       <c r="B15" t="n">
-        <v>56765</v>
+        <v>81862</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,39 +2157,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544419</v>
+        <v>544013</v>
       </c>
       <c r="R15" t="n">
-        <v>7208372</v>
+        <v>7208532</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188894</v>
+        <v>113188878</v>
       </c>
       <c r="B16" t="n">
-        <v>78105</v>
+        <v>90063</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,21 +2269,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544427</v>
+        <v>544229</v>
       </c>
       <c r="R16" t="n">
-        <v>7208357</v>
+        <v>7208430</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2338,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188872</v>
+        <v>113188895</v>
       </c>
       <c r="B17" t="n">
-        <v>77086</v>
+        <v>78121</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,21 +2381,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2415,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544389</v>
+        <v>544444</v>
       </c>
       <c r="R17" t="n">
-        <v>7208365</v>
+        <v>7208349</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188881</v>
+        <v>113188885</v>
       </c>
       <c r="B18" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543877</v>
+        <v>544156</v>
       </c>
       <c r="R18" t="n">
-        <v>7208540</v>
+        <v>7208494</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188857</v>
+        <v>113188858</v>
       </c>
       <c r="B19" t="n">
-        <v>74286</v>
+        <v>74302</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544013</v>
+        <v>544389</v>
       </c>
       <c r="R19" t="n">
-        <v>7208532</v>
+        <v>7208368</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2674,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188891</v>
+        <v>113188872</v>
       </c>
       <c r="B20" t="n">
-        <v>78105</v>
+        <v>77102</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2786,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188879</v>
+        <v>113188860</v>
       </c>
       <c r="B21" t="n">
-        <v>90047</v>
+        <v>56765</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,34 +2829,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544428</v>
+        <v>543868</v>
       </c>
       <c r="R21" t="n">
-        <v>7208357</v>
+        <v>7208522</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2898,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,10 +2930,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188869</v>
+        <v>113188863</v>
       </c>
       <c r="B22" t="n">
-        <v>74291</v>
+        <v>56765</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,34 +2946,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544425</v>
+        <v>544344</v>
       </c>
       <c r="R22" t="n">
-        <v>7208380</v>
+        <v>7208412</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188898</v>
+        <v>113188859</v>
       </c>
       <c r="B23" t="n">
-        <v>81846</v>
+        <v>90045</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544013</v>
+        <v>543970</v>
       </c>
       <c r="R23" t="n">
-        <v>7208532</v>
+        <v>7208507</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188877</v>
+        <v>113188886</v>
       </c>
       <c r="B24" t="n">
-        <v>90047</v>
+        <v>78121</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,21 +3175,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543877</v>
+        <v>544163</v>
       </c>
       <c r="R24" t="n">
-        <v>7208540</v>
+        <v>7208441</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188860</v>
+        <v>113188873</v>
       </c>
       <c r="B25" t="n">
-        <v>56765</v>
+        <v>77478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,43 +3283,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543868</v>
+        <v>544156</v>
       </c>
       <c r="R25" t="n">
-        <v>7208522</v>
+        <v>7208494</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3351,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188873</v>
+        <v>113188890</v>
       </c>
       <c r="B26" t="n">
-        <v>77462</v>
+        <v>78121</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3400,25 +3395,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3428,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544156</v>
+        <v>544344</v>
       </c>
       <c r="R26" t="n">
-        <v>7208494</v>
+        <v>7208412</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3463,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3468,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,10 +3495,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113188858</v>
+        <v>113188875</v>
       </c>
       <c r="B27" t="n">
-        <v>74286</v>
+        <v>78202</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3516,21 +3511,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3540,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544389</v>
+        <v>544013</v>
       </c>
       <c r="R27" t="n">
-        <v>7208368</v>
+        <v>7208532</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3575,7 +3570,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3585,7 +3580,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,10 +3607,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113188885</v>
+        <v>113188882</v>
       </c>
       <c r="B28" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3652,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544156</v>
+        <v>543905</v>
       </c>
       <c r="R28" t="n">
-        <v>7208494</v>
+        <v>7208555</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3687,7 +3682,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,7 +3692,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3724,10 +3719,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113188889</v>
+        <v>113188869</v>
       </c>
       <c r="B29" t="n">
-        <v>78105</v>
+        <v>74307</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3740,21 +3735,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3764,10 +3759,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544243</v>
+        <v>544425</v>
       </c>
       <c r="R29" t="n">
-        <v>7208437</v>
+        <v>7208380</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,10 +3831,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113188883</v>
+        <v>113188857</v>
       </c>
       <c r="B30" t="n">
-        <v>78105</v>
+        <v>74302</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3852,21 +3847,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3876,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543970</v>
+        <v>544013</v>
       </c>
       <c r="R30" t="n">
-        <v>7208506</v>
+        <v>7208532</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3911,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113188863</v>
+        <v>113188884</v>
       </c>
       <c r="B31" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,39 +3959,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544344</v>
+        <v>544013</v>
       </c>
       <c r="R31" t="n">
-        <v>7208412</v>
+        <v>7208532</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4028,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113188876</v>
+        <v>113188881</v>
       </c>
       <c r="B32" t="n">
-        <v>90025</v>
+        <v>78121</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4081,21 +4071,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4105,10 +4095,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544013</v>
+        <v>543877</v>
       </c>
       <c r="R32" t="n">
-        <v>7208531</v>
+        <v>7208540</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4140,7 +4130,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4140,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,10 +4167,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113188893</v>
+        <v>113188861</v>
       </c>
       <c r="B33" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4193,34 +4183,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544429</v>
+        <v>544162</v>
       </c>
       <c r="R33" t="n">
-        <v>7208373</v>
+        <v>7208445</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4252,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4257,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -1912,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188865</v>
+        <v>113188879</v>
       </c>
       <c r="B13" t="n">
-        <v>56765</v>
+        <v>90063</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,39 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544430</v>
+        <v>544428</v>
       </c>
       <c r="R13" t="n">
-        <v>7208372</v>
+        <v>7208357</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188879</v>
+        <v>113188865</v>
       </c>
       <c r="B14" t="n">
-        <v>90063</v>
+        <v>56765</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,34 +2040,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544428</v>
+        <v>544430</v>
       </c>
       <c r="R14" t="n">
-        <v>7208357</v>
+        <v>7208372</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188880</v>
+        <v>113188857</v>
       </c>
       <c r="B2" t="n">
-        <v>78121</v>
+        <v>74302</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543869</v>
+        <v>544013</v>
       </c>
       <c r="R2" t="n">
-        <v>7208524</v>
+        <v>7208532</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188891</v>
+        <v>113188888</v>
       </c>
       <c r="B3" t="n">
         <v>78121</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544389</v>
+        <v>544228</v>
       </c>
       <c r="R3" t="n">
-        <v>7208365</v>
+        <v>7208430</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188888</v>
+        <v>113188884</v>
       </c>
       <c r="B4" t="n">
         <v>78121</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544228</v>
+        <v>544013</v>
       </c>
       <c r="R4" t="n">
-        <v>7208430</v>
+        <v>7208532</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188894</v>
+        <v>113188872</v>
       </c>
       <c r="B5" t="n">
-        <v>78121</v>
+        <v>77102</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544427</v>
+        <v>544389</v>
       </c>
       <c r="R5" t="n">
-        <v>7208357</v>
+        <v>7208365</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188877</v>
+        <v>113188893</v>
       </c>
       <c r="B6" t="n">
-        <v>90063</v>
+        <v>78121</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543877</v>
+        <v>544429</v>
       </c>
       <c r="R6" t="n">
-        <v>7208540</v>
+        <v>7208373</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188889</v>
+        <v>113188881</v>
       </c>
       <c r="B7" t="n">
         <v>78121</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544243</v>
+        <v>543877</v>
       </c>
       <c r="R7" t="n">
-        <v>7208437</v>
+        <v>7208540</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188892</v>
+        <v>113188879</v>
       </c>
       <c r="B8" t="n">
-        <v>78121</v>
+        <v>90063</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544425</v>
+        <v>544428</v>
       </c>
       <c r="R8" t="n">
-        <v>7208367</v>
+        <v>7208357</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188883</v>
+        <v>113188869</v>
       </c>
       <c r="B9" t="n">
-        <v>78121</v>
+        <v>74307</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543970</v>
+        <v>544425</v>
       </c>
       <c r="R9" t="n">
-        <v>7208506</v>
+        <v>7208380</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188876</v>
+        <v>113188898</v>
       </c>
       <c r="B10" t="n">
-        <v>90041</v>
+        <v>81862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
         <v>544013</v>
       </c>
       <c r="R10" t="n">
-        <v>7208531</v>
+        <v>7208532</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188893</v>
+        <v>113188861</v>
       </c>
       <c r="B11" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,34 +1699,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544429</v>
+        <v>544162</v>
       </c>
       <c r="R11" t="n">
-        <v>7208373</v>
+        <v>7208445</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1773,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1805,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188864</v>
+        <v>113188863</v>
       </c>
       <c r="B12" t="n">
         <v>56765</v>
@@ -1840,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544419</v>
+        <v>544344</v>
       </c>
       <c r="R12" t="n">
-        <v>7208372</v>
+        <v>7208412</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188879</v>
+        <v>113188859</v>
       </c>
       <c r="B13" t="n">
-        <v>90063</v>
+        <v>90045</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544428</v>
+        <v>543970</v>
       </c>
       <c r="R13" t="n">
-        <v>7208357</v>
+        <v>7208507</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188865</v>
+        <v>113188886</v>
       </c>
       <c r="B14" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,39 +2050,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544430</v>
+        <v>544163</v>
       </c>
       <c r="R14" t="n">
-        <v>7208372</v>
+        <v>7208441</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188898</v>
+        <v>113188891</v>
       </c>
       <c r="B15" t="n">
-        <v>81862</v>
+        <v>78121</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544013</v>
+        <v>544389</v>
       </c>
       <c r="R15" t="n">
-        <v>7208532</v>
+        <v>7208365</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188878</v>
+        <v>113188875</v>
       </c>
       <c r="B16" t="n">
-        <v>90063</v>
+        <v>78202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,21 +2274,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544229</v>
+        <v>544013</v>
       </c>
       <c r="R16" t="n">
-        <v>7208430</v>
+        <v>7208532</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188895</v>
+        <v>113188877</v>
       </c>
       <c r="B17" t="n">
-        <v>78121</v>
+        <v>90063</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,21 +2386,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544444</v>
+        <v>543877</v>
       </c>
       <c r="R17" t="n">
-        <v>7208349</v>
+        <v>7208540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188885</v>
+        <v>113188860</v>
       </c>
       <c r="B18" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,34 +2498,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544156</v>
+        <v>543868</v>
       </c>
       <c r="R18" t="n">
-        <v>7208494</v>
+        <v>7208522</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188858</v>
+        <v>113188880</v>
       </c>
       <c r="B19" t="n">
-        <v>74302</v>
+        <v>78121</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,21 +2615,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544389</v>
+        <v>543869</v>
       </c>
       <c r="R19" t="n">
-        <v>7208368</v>
+        <v>7208524</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188872</v>
+        <v>113188892</v>
       </c>
       <c r="B20" t="n">
-        <v>77102</v>
+        <v>78121</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,21 +2727,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544389</v>
+        <v>544425</v>
       </c>
       <c r="R20" t="n">
-        <v>7208365</v>
+        <v>7208367</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188860</v>
+        <v>113188873</v>
       </c>
       <c r="B21" t="n">
-        <v>56765</v>
+        <v>77478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,43 +2835,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543868</v>
+        <v>544156</v>
       </c>
       <c r="R21" t="n">
-        <v>7208522</v>
+        <v>7208494</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2893,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188863</v>
+        <v>113188878</v>
       </c>
       <c r="B22" t="n">
-        <v>56765</v>
+        <v>90063</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,39 +2951,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544344</v>
+        <v>544229</v>
       </c>
       <c r="R22" t="n">
-        <v>7208412</v>
+        <v>7208430</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188859</v>
+        <v>113188864</v>
       </c>
       <c r="B23" t="n">
-        <v>90045</v>
+        <v>56765</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,34 +3063,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543970</v>
+        <v>544419</v>
       </c>
       <c r="R23" t="n">
-        <v>7208507</v>
+        <v>7208372</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188886</v>
+        <v>113188858</v>
       </c>
       <c r="B24" t="n">
-        <v>78121</v>
+        <v>74302</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,21 +3180,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544163</v>
+        <v>544389</v>
       </c>
       <c r="R24" t="n">
-        <v>7208441</v>
+        <v>7208368</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3234,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188873</v>
+        <v>113188885</v>
       </c>
       <c r="B25" t="n">
-        <v>77478</v>
+        <v>78121</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,25 +3288,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3346,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3383,7 +3388,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188890</v>
+        <v>113188889</v>
       </c>
       <c r="B26" t="n">
         <v>78121</v>
@@ -3423,10 +3428,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544344</v>
+        <v>544243</v>
       </c>
       <c r="R26" t="n">
-        <v>7208412</v>
+        <v>7208437</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3458,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,10 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113188875</v>
+        <v>113188890</v>
       </c>
       <c r="B27" t="n">
-        <v>78202</v>
+        <v>78121</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3511,21 +3516,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3535,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544013</v>
+        <v>544344</v>
       </c>
       <c r="R27" t="n">
-        <v>7208532</v>
+        <v>7208412</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3570,7 +3575,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3580,7 +3585,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3607,10 +3612,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113188882</v>
+        <v>113188876</v>
       </c>
       <c r="B28" t="n">
-        <v>78121</v>
+        <v>90041</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3623,21 +3628,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3647,10 +3652,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543905</v>
+        <v>544013</v>
       </c>
       <c r="R28" t="n">
-        <v>7208555</v>
+        <v>7208531</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3682,7 +3687,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3692,7 +3697,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3719,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113188869</v>
+        <v>113188895</v>
       </c>
       <c r="B29" t="n">
-        <v>74307</v>
+        <v>78121</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3735,21 +3740,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3759,10 +3764,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544425</v>
+        <v>544444</v>
       </c>
       <c r="R29" t="n">
-        <v>7208380</v>
+        <v>7208349</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,10 +3836,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113188857</v>
+        <v>113188883</v>
       </c>
       <c r="B30" t="n">
-        <v>74302</v>
+        <v>78121</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3847,21 +3852,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3871,10 +3876,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544013</v>
+        <v>543970</v>
       </c>
       <c r="R30" t="n">
-        <v>7208532</v>
+        <v>7208506</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3906,7 +3911,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3921,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,7 +3948,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113188884</v>
+        <v>113188894</v>
       </c>
       <c r="B31" t="n">
         <v>78121</v>
@@ -3983,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544013</v>
+        <v>544427</v>
       </c>
       <c r="R31" t="n">
-        <v>7208532</v>
+        <v>7208357</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4028,7 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4055,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113188881</v>
+        <v>113188865</v>
       </c>
       <c r="B32" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4071,34 +4076,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543877</v>
+        <v>544430</v>
       </c>
       <c r="R32" t="n">
-        <v>7208540</v>
+        <v>7208372</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4130,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4140,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113188861</v>
+        <v>113188882</v>
       </c>
       <c r="B33" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4183,39 +4193,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544162</v>
+        <v>543905</v>
       </c>
       <c r="R33" t="n">
-        <v>7208445</v>
+        <v>7208555</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4247,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,12 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188857</v>
+        <v>113188879</v>
       </c>
       <c r="B2" t="n">
-        <v>74302</v>
+        <v>90075</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544013</v>
+        <v>544428</v>
       </c>
       <c r="R2" t="n">
-        <v>7208532</v>
+        <v>7208357</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188888</v>
+        <v>113188878</v>
       </c>
       <c r="B3" t="n">
-        <v>78121</v>
+        <v>90075</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544228</v>
+        <v>544229</v>
       </c>
       <c r="R3" t="n">
         <v>7208430</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188884</v>
+        <v>113188892</v>
       </c>
       <c r="B4" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544013</v>
+        <v>544425</v>
       </c>
       <c r="R4" t="n">
-        <v>7208532</v>
+        <v>7208367</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>113188872</v>
       </c>
       <c r="B5" t="n">
-        <v>77102</v>
+        <v>77114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188893</v>
+        <v>113188869</v>
       </c>
       <c r="B6" t="n">
-        <v>78121</v>
+        <v>74319</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544429</v>
+        <v>544425</v>
       </c>
       <c r="R6" t="n">
-        <v>7208373</v>
+        <v>7208380</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188881</v>
+        <v>113188883</v>
       </c>
       <c r="B7" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543877</v>
+        <v>543970</v>
       </c>
       <c r="R7" t="n">
-        <v>7208540</v>
+        <v>7208506</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188879</v>
+        <v>113188885</v>
       </c>
       <c r="B8" t="n">
-        <v>90063</v>
+        <v>78133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544428</v>
+        <v>544156</v>
       </c>
       <c r="R8" t="n">
-        <v>7208357</v>
+        <v>7208494</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188869</v>
+        <v>113188857</v>
       </c>
       <c r="B9" t="n">
-        <v>74307</v>
+        <v>74314</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544425</v>
+        <v>544013</v>
       </c>
       <c r="R9" t="n">
-        <v>7208380</v>
+        <v>7208532</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188898</v>
+        <v>113188863</v>
       </c>
       <c r="B10" t="n">
-        <v>81862</v>
+        <v>56766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,34 +1587,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544013</v>
+        <v>544344</v>
       </c>
       <c r="R10" t="n">
-        <v>7208532</v>
+        <v>7208412</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188861</v>
+        <v>113188880</v>
       </c>
       <c r="B11" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,39 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544162</v>
+        <v>543869</v>
       </c>
       <c r="R11" t="n">
-        <v>7208445</v>
+        <v>7208524</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,12 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188863</v>
+        <v>113188894</v>
       </c>
       <c r="B12" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,39 +1816,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544344</v>
+        <v>544427</v>
       </c>
       <c r="R12" t="n">
-        <v>7208412</v>
+        <v>7208357</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,7 +1915,7 @@
         <v>113188859</v>
       </c>
       <c r="B13" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2034,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188886</v>
+        <v>113188858</v>
       </c>
       <c r="B14" t="n">
-        <v>78121</v>
+        <v>74314</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2040,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544163</v>
+        <v>544389</v>
       </c>
       <c r="R14" t="n">
-        <v>7208441</v>
+        <v>7208368</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188891</v>
+        <v>113188886</v>
       </c>
       <c r="B15" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544389</v>
+        <v>544163</v>
       </c>
       <c r="R15" t="n">
-        <v>7208365</v>
+        <v>7208441</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188875</v>
+        <v>113188882</v>
       </c>
       <c r="B16" t="n">
-        <v>78202</v>
+        <v>78133</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544013</v>
+        <v>543905</v>
       </c>
       <c r="R16" t="n">
-        <v>7208532</v>
+        <v>7208555</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188877</v>
+        <v>113188876</v>
       </c>
       <c r="B17" t="n">
-        <v>90063</v>
+        <v>90053</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2410,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543877</v>
+        <v>544013</v>
       </c>
       <c r="R17" t="n">
-        <v>7208540</v>
+        <v>7208531</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2445,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188860</v>
+        <v>113188877</v>
       </c>
       <c r="B18" t="n">
-        <v>56765</v>
+        <v>90075</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,39 +2488,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543868</v>
+        <v>543877</v>
       </c>
       <c r="R18" t="n">
-        <v>7208522</v>
+        <v>7208540</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188880</v>
+        <v>113188861</v>
       </c>
       <c r="B19" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,34 +2600,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543869</v>
+        <v>544162</v>
       </c>
       <c r="R19" t="n">
-        <v>7208524</v>
+        <v>7208445</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2674,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2674,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188892</v>
+        <v>113188890</v>
       </c>
       <c r="B20" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2751,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544425</v>
+        <v>544344</v>
       </c>
       <c r="R20" t="n">
-        <v>7208367</v>
+        <v>7208412</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2786,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188873</v>
+        <v>113188864</v>
       </c>
       <c r="B21" t="n">
-        <v>77478</v>
+        <v>56766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2835,38 +2830,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544156</v>
+        <v>544419</v>
       </c>
       <c r="R21" t="n">
-        <v>7208494</v>
+        <v>7208372</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188878</v>
+        <v>113188873</v>
       </c>
       <c r="B22" t="n">
-        <v>90063</v>
+        <v>77490</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,25 +2947,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544229</v>
+        <v>544156</v>
       </c>
       <c r="R22" t="n">
-        <v>7208430</v>
+        <v>7208494</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188864</v>
+        <v>113188888</v>
       </c>
       <c r="B23" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,39 +3063,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544419</v>
+        <v>544228</v>
       </c>
       <c r="R23" t="n">
-        <v>7208372</v>
+        <v>7208430</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188858</v>
+        <v>113188895</v>
       </c>
       <c r="B24" t="n">
-        <v>74302</v>
+        <v>78133</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,21 +3175,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3204,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544389</v>
+        <v>544444</v>
       </c>
       <c r="R24" t="n">
-        <v>7208368</v>
+        <v>7208349</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188885</v>
+        <v>113188891</v>
       </c>
       <c r="B25" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3316,10 +3311,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544156</v>
+        <v>544389</v>
       </c>
       <c r="R25" t="n">
-        <v>7208494</v>
+        <v>7208365</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3351,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3391,7 +3386,7 @@
         <v>113188889</v>
       </c>
       <c r="B26" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3500,10 +3495,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113188890</v>
+        <v>113188875</v>
       </c>
       <c r="B27" t="n">
-        <v>78121</v>
+        <v>78214</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3516,21 +3511,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3540,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544344</v>
+        <v>544013</v>
       </c>
       <c r="R27" t="n">
-        <v>7208412</v>
+        <v>7208532</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3575,7 +3570,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3585,7 +3580,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,10 +3607,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113188876</v>
+        <v>113188893</v>
       </c>
       <c r="B28" t="n">
-        <v>90041</v>
+        <v>78133</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3628,21 +3623,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3652,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544013</v>
+        <v>544429</v>
       </c>
       <c r="R28" t="n">
-        <v>7208531</v>
+        <v>7208373</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3687,7 +3682,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,7 +3692,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3724,10 +3719,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113188895</v>
+        <v>113188898</v>
       </c>
       <c r="B29" t="n">
-        <v>78121</v>
+        <v>81874</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3740,21 +3735,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3764,10 +3759,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544444</v>
+        <v>544013</v>
       </c>
       <c r="R29" t="n">
-        <v>7208349</v>
+        <v>7208532</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,10 +3831,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113188883</v>
+        <v>113188884</v>
       </c>
       <c r="B30" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543970</v>
+        <v>544013</v>
       </c>
       <c r="R30" t="n">
-        <v>7208506</v>
+        <v>7208532</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3911,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113188894</v>
+        <v>113188881</v>
       </c>
       <c r="B31" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3988,10 +3983,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544427</v>
+        <v>543877</v>
       </c>
       <c r="R31" t="n">
-        <v>7208357</v>
+        <v>7208540</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4023,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4063,7 +4058,7 @@
         <v>113188865</v>
       </c>
       <c r="B32" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4177,10 +4172,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113188882</v>
+        <v>113188860</v>
       </c>
       <c r="B33" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4193,34 +4188,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543905</v>
+        <v>543868</v>
       </c>
       <c r="R33" t="n">
-        <v>7208555</v>
+        <v>7208522</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188879</v>
+        <v>113188893</v>
       </c>
       <c r="B2" t="n">
-        <v>90075</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544428</v>
+        <v>544429</v>
       </c>
       <c r="R2" t="n">
-        <v>7208357</v>
+        <v>7208373</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188878</v>
+        <v>113188864</v>
       </c>
       <c r="B3" t="n">
-        <v>90075</v>
+        <v>56766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544229</v>
+        <v>544419</v>
       </c>
       <c r="R3" t="n">
-        <v>7208430</v>
+        <v>7208372</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188892</v>
+        <v>113188863</v>
       </c>
       <c r="B4" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544425</v>
+        <v>544344</v>
       </c>
       <c r="R4" t="n">
-        <v>7208367</v>
+        <v>7208412</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188872</v>
+        <v>113188861</v>
       </c>
       <c r="B5" t="n">
-        <v>77114</v>
+        <v>56766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544389</v>
+        <v>544162</v>
       </c>
       <c r="R5" t="n">
-        <v>7208365</v>
+        <v>7208445</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188869</v>
+        <v>113188885</v>
       </c>
       <c r="B6" t="n">
-        <v>74319</v>
+        <v>78133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544425</v>
+        <v>544156</v>
       </c>
       <c r="R6" t="n">
-        <v>7208380</v>
+        <v>7208494</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188883</v>
+        <v>113188882</v>
       </c>
       <c r="B7" t="n">
         <v>78133</v>
@@ -1275,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543970</v>
+        <v>543905</v>
       </c>
       <c r="R7" t="n">
-        <v>7208506</v>
+        <v>7208555</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188885</v>
+        <v>113188886</v>
       </c>
       <c r="B8" t="n">
         <v>78133</v>
@@ -1387,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544156</v>
+        <v>544163</v>
       </c>
       <c r="R8" t="n">
-        <v>7208494</v>
+        <v>7208441</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188857</v>
+        <v>113188869</v>
       </c>
       <c r="B9" t="n">
-        <v>74314</v>
+        <v>74319</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544013</v>
+        <v>544425</v>
       </c>
       <c r="R9" t="n">
-        <v>7208532</v>
+        <v>7208380</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188863</v>
+        <v>113188888</v>
       </c>
       <c r="B10" t="n">
-        <v>56766</v>
+        <v>78133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544344</v>
+        <v>544228</v>
       </c>
       <c r="R10" t="n">
-        <v>7208412</v>
+        <v>7208430</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188880</v>
+        <v>113188883</v>
       </c>
       <c r="B11" t="n">
         <v>78133</v>
@@ -1728,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543869</v>
+        <v>543970</v>
       </c>
       <c r="R11" t="n">
-        <v>7208524</v>
+        <v>7208506</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188894</v>
+        <v>113188858</v>
       </c>
       <c r="B12" t="n">
-        <v>78133</v>
+        <v>74314</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544427</v>
+        <v>544389</v>
       </c>
       <c r="R12" t="n">
-        <v>7208357</v>
+        <v>7208368</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188859</v>
+        <v>113188892</v>
       </c>
       <c r="B13" t="n">
-        <v>90057</v>
+        <v>78133</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1943,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543970</v>
+        <v>544425</v>
       </c>
       <c r="R13" t="n">
-        <v>7208507</v>
+        <v>7208367</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188858</v>
+        <v>113188877</v>
       </c>
       <c r="B14" t="n">
-        <v>74314</v>
+        <v>90075</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,21 +2055,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544389</v>
+        <v>543877</v>
       </c>
       <c r="R14" t="n">
-        <v>7208368</v>
+        <v>7208540</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188886</v>
+        <v>113188878</v>
       </c>
       <c r="B15" t="n">
-        <v>78133</v>
+        <v>90075</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2167,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544163</v>
+        <v>544229</v>
       </c>
       <c r="R15" t="n">
-        <v>7208441</v>
+        <v>7208430</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,7 +2263,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188882</v>
+        <v>113188890</v>
       </c>
       <c r="B16" t="n">
         <v>78133</v>
@@ -2288,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543905</v>
+        <v>544344</v>
       </c>
       <c r="R16" t="n">
-        <v>7208555</v>
+        <v>7208412</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188876</v>
+        <v>113188889</v>
       </c>
       <c r="B17" t="n">
-        <v>90053</v>
+        <v>78133</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,21 +2391,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544013</v>
+        <v>544243</v>
       </c>
       <c r="R17" t="n">
-        <v>7208531</v>
+        <v>7208437</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188877</v>
+        <v>113188891</v>
       </c>
       <c r="B18" t="n">
-        <v>90075</v>
+        <v>78133</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,21 +2503,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543877</v>
+        <v>544389</v>
       </c>
       <c r="R18" t="n">
-        <v>7208540</v>
+        <v>7208365</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188861</v>
+        <v>113188872</v>
       </c>
       <c r="B19" t="n">
-        <v>56766</v>
+        <v>77114</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,39 +2615,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544162</v>
+        <v>544389</v>
       </c>
       <c r="R19" t="n">
-        <v>7208445</v>
+        <v>7208365</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,12 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188890</v>
+        <v>113188898</v>
       </c>
       <c r="B20" t="n">
-        <v>78133</v>
+        <v>81874</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,21 +2727,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2746,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544344</v>
+        <v>544013</v>
       </c>
       <c r="R20" t="n">
-        <v>7208412</v>
+        <v>7208532</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188864</v>
+        <v>113188873</v>
       </c>
       <c r="B21" t="n">
-        <v>56766</v>
+        <v>77490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2830,43 +2835,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544419</v>
+        <v>544156</v>
       </c>
       <c r="R21" t="n">
-        <v>7208372</v>
+        <v>7208494</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188873</v>
+        <v>113188876</v>
       </c>
       <c r="B22" t="n">
-        <v>77490</v>
+        <v>90053</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,25 +2947,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>498</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544156</v>
+        <v>544013</v>
       </c>
       <c r="R22" t="n">
-        <v>7208494</v>
+        <v>7208531</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188888</v>
+        <v>113188865</v>
       </c>
       <c r="B23" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,34 +3063,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544228</v>
+        <v>544430</v>
       </c>
       <c r="R23" t="n">
-        <v>7208430</v>
+        <v>7208372</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188895</v>
+        <v>113188875</v>
       </c>
       <c r="B24" t="n">
-        <v>78133</v>
+        <v>78214</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,21 +3180,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544444</v>
+        <v>544013</v>
       </c>
       <c r="R24" t="n">
-        <v>7208349</v>
+        <v>7208532</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3234,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,7 +3276,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188891</v>
+        <v>113188880</v>
       </c>
       <c r="B25" t="n">
         <v>78133</v>
@@ -3311,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544389</v>
+        <v>543869</v>
       </c>
       <c r="R25" t="n">
-        <v>7208365</v>
+        <v>7208524</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3346,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3383,7 +3388,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188889</v>
+        <v>113188881</v>
       </c>
       <c r="B26" t="n">
         <v>78133</v>
@@ -3423,10 +3428,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544243</v>
+        <v>543877</v>
       </c>
       <c r="R26" t="n">
-        <v>7208437</v>
+        <v>7208540</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3458,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,10 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113188875</v>
+        <v>113188895</v>
       </c>
       <c r="B27" t="n">
-        <v>78214</v>
+        <v>78133</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3511,21 +3516,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3535,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544013</v>
+        <v>544444</v>
       </c>
       <c r="R27" t="n">
-        <v>7208532</v>
+        <v>7208349</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3570,7 +3575,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3580,7 +3585,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3607,10 +3612,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113188893</v>
+        <v>113188857</v>
       </c>
       <c r="B28" t="n">
-        <v>78133</v>
+        <v>74314</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3623,21 +3628,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3647,10 +3652,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544429</v>
+        <v>544013</v>
       </c>
       <c r="R28" t="n">
-        <v>7208373</v>
+        <v>7208532</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3682,7 +3687,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3692,7 +3697,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3719,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113188898</v>
+        <v>113188884</v>
       </c>
       <c r="B29" t="n">
-        <v>81874</v>
+        <v>78133</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3735,21 +3740,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3831,7 +3836,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113188884</v>
+        <v>113188894</v>
       </c>
       <c r="B30" t="n">
         <v>78133</v>
@@ -3871,10 +3876,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544013</v>
+        <v>544427</v>
       </c>
       <c r="R30" t="n">
-        <v>7208532</v>
+        <v>7208357</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3906,7 +3911,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3921,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113188881</v>
+        <v>113188859</v>
       </c>
       <c r="B31" t="n">
-        <v>78133</v>
+        <v>90057</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,21 +3964,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3983,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543877</v>
+        <v>543970</v>
       </c>
       <c r="R31" t="n">
-        <v>7208540</v>
+        <v>7208507</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4028,7 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4055,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113188865</v>
+        <v>113188879</v>
       </c>
       <c r="B32" t="n">
-        <v>56766</v>
+        <v>90075</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4071,39 +4076,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544430</v>
+        <v>544428</v>
       </c>
       <c r="R32" t="n">
-        <v>7208372</v>
+        <v>7208357</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188882</v>
+        <v>113188869</v>
       </c>
       <c r="B7" t="n">
-        <v>78133</v>
+        <v>74319</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543905</v>
+        <v>544425</v>
       </c>
       <c r="R7" t="n">
-        <v>7208555</v>
+        <v>7208380</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188886</v>
+        <v>113188882</v>
       </c>
       <c r="B8" t="n">
         <v>78133</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544163</v>
+        <v>543905</v>
       </c>
       <c r="R8" t="n">
-        <v>7208441</v>
+        <v>7208555</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188869</v>
+        <v>113188886</v>
       </c>
       <c r="B9" t="n">
-        <v>74319</v>
+        <v>78133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544425</v>
+        <v>544163</v>
       </c>
       <c r="R9" t="n">
-        <v>7208380</v>
+        <v>7208441</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188888</v>
+        <v>113188858</v>
       </c>
       <c r="B10" t="n">
-        <v>78133</v>
+        <v>74314</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544228</v>
+        <v>544389</v>
       </c>
       <c r="R10" t="n">
-        <v>7208430</v>
+        <v>7208368</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188883</v>
+        <v>113188888</v>
       </c>
       <c r="B11" t="n">
         <v>78133</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543970</v>
+        <v>544228</v>
       </c>
       <c r="R11" t="n">
-        <v>7208506</v>
+        <v>7208430</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188858</v>
+        <v>113188883</v>
       </c>
       <c r="B12" t="n">
-        <v>74314</v>
+        <v>78133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544389</v>
+        <v>543970</v>
       </c>
       <c r="R12" t="n">
-        <v>7208368</v>
+        <v>7208506</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188891</v>
+        <v>113188873</v>
       </c>
       <c r="B18" t="n">
-        <v>78133</v>
+        <v>77490</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,25 +2499,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544389</v>
+        <v>544156</v>
       </c>
       <c r="R18" t="n">
-        <v>7208365</v>
+        <v>7208494</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2823,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188873</v>
+        <v>113188891</v>
       </c>
       <c r="B21" t="n">
-        <v>77490</v>
+        <v>78133</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2835,25 +2835,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544156</v>
+        <v>544389</v>
       </c>
       <c r="R21" t="n">
-        <v>7208494</v>
+        <v>7208365</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188876</v>
+        <v>113188875</v>
       </c>
       <c r="B22" t="n">
-        <v>90053</v>
+        <v>78214</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,21 +2951,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2978,7 +2978,7 @@
         <v>544013</v>
       </c>
       <c r="R22" t="n">
-        <v>7208531</v>
+        <v>7208532</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188875</v>
+        <v>113188876</v>
       </c>
       <c r="B24" t="n">
-        <v>78214</v>
+        <v>90053</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,21 +3180,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
         <v>544013</v>
       </c>
       <c r="R24" t="n">
-        <v>7208532</v>
+        <v>7208531</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188893</v>
+        <v>113188880</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544429</v>
+        <v>543869</v>
       </c>
       <c r="R2" t="n">
-        <v>7208373</v>
+        <v>7208524</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188864</v>
+        <v>113188898</v>
       </c>
       <c r="B3" t="n">
-        <v>56766</v>
+        <v>81896</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544419</v>
+        <v>544013</v>
       </c>
       <c r="R3" t="n">
-        <v>7208372</v>
+        <v>7208532</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188863</v>
+        <v>113188860</v>
       </c>
       <c r="B4" t="n">
         <v>56766</v>
@@ -940,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544344</v>
+        <v>543868</v>
       </c>
       <c r="R4" t="n">
-        <v>7208412</v>
+        <v>7208522</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188861</v>
+        <v>113188891</v>
       </c>
       <c r="B5" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544162</v>
+        <v>544389</v>
       </c>
       <c r="R5" t="n">
-        <v>7208445</v>
+        <v>7208365</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188885</v>
+        <v>113188878</v>
       </c>
       <c r="B6" t="n">
-        <v>78133</v>
+        <v>90097</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544156</v>
+        <v>544229</v>
       </c>
       <c r="R6" t="n">
-        <v>7208494</v>
+        <v>7208430</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188869</v>
+        <v>113188890</v>
       </c>
       <c r="B7" t="n">
-        <v>74319</v>
+        <v>78155</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544425</v>
+        <v>544344</v>
       </c>
       <c r="R7" t="n">
-        <v>7208380</v>
+        <v>7208412</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188882</v>
+        <v>113188881</v>
       </c>
       <c r="B8" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543905</v>
+        <v>543877</v>
       </c>
       <c r="R8" t="n">
-        <v>7208555</v>
+        <v>7208540</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188886</v>
+        <v>113188892</v>
       </c>
       <c r="B9" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544163</v>
+        <v>544425</v>
       </c>
       <c r="R9" t="n">
-        <v>7208441</v>
+        <v>7208367</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188858</v>
+        <v>113188864</v>
       </c>
       <c r="B10" t="n">
-        <v>74314</v>
+        <v>56766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,34 +1592,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544389</v>
+        <v>544419</v>
       </c>
       <c r="R10" t="n">
-        <v>7208368</v>
+        <v>7208372</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188888</v>
+        <v>113188886</v>
       </c>
       <c r="B11" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544228</v>
+        <v>544163</v>
       </c>
       <c r="R11" t="n">
-        <v>7208430</v>
+        <v>7208441</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188883</v>
+        <v>113188877</v>
       </c>
       <c r="B12" t="n">
-        <v>78133</v>
+        <v>90097</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543970</v>
+        <v>543877</v>
       </c>
       <c r="R12" t="n">
-        <v>7208506</v>
+        <v>7208540</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188892</v>
+        <v>113188869</v>
       </c>
       <c r="B13" t="n">
-        <v>78133</v>
+        <v>74341</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,21 +1933,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1970,7 +1960,7 @@
         <v>544425</v>
       </c>
       <c r="R13" t="n">
-        <v>7208367</v>
+        <v>7208380</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188877</v>
+        <v>113188885</v>
       </c>
       <c r="B14" t="n">
-        <v>90075</v>
+        <v>78155</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,21 +2045,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2079,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543877</v>
+        <v>544156</v>
       </c>
       <c r="R14" t="n">
-        <v>7208540</v>
+        <v>7208494</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188878</v>
+        <v>113188888</v>
       </c>
       <c r="B15" t="n">
-        <v>90075</v>
+        <v>78155</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,21 +2157,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2191,7 +2181,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544229</v>
+        <v>544228</v>
       </c>
       <c r="R15" t="n">
         <v>7208430</v>
@@ -2263,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188890</v>
+        <v>113188894</v>
       </c>
       <c r="B16" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544344</v>
+        <v>544427</v>
       </c>
       <c r="R16" t="n">
-        <v>7208412</v>
+        <v>7208357</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2338,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188889</v>
+        <v>113188858</v>
       </c>
       <c r="B17" t="n">
-        <v>78133</v>
+        <v>74336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,21 +2381,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2415,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544243</v>
+        <v>544389</v>
       </c>
       <c r="R17" t="n">
-        <v>7208437</v>
+        <v>7208368</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188873</v>
+        <v>113188859</v>
       </c>
       <c r="B18" t="n">
-        <v>77490</v>
+        <v>90079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,25 +2489,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>498</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2527,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544156</v>
+        <v>543970</v>
       </c>
       <c r="R18" t="n">
-        <v>7208494</v>
+        <v>7208507</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188872</v>
+        <v>113188861</v>
       </c>
       <c r="B19" t="n">
-        <v>77114</v>
+        <v>56766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,34 +2605,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544389</v>
+        <v>544162</v>
       </c>
       <c r="R19" t="n">
-        <v>7208365</v>
+        <v>7208445</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2674,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2679,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188898</v>
+        <v>113188875</v>
       </c>
       <c r="B20" t="n">
-        <v>81874</v>
+        <v>78236</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,21 +2727,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188891</v>
+        <v>113188863</v>
       </c>
       <c r="B21" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,34 +2839,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544389</v>
+        <v>544344</v>
       </c>
       <c r="R21" t="n">
-        <v>7208365</v>
+        <v>7208412</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2898,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188875</v>
+        <v>113188876</v>
       </c>
       <c r="B22" t="n">
-        <v>78214</v>
+        <v>90075</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,21 +2956,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2978,7 +2983,7 @@
         <v>544013</v>
       </c>
       <c r="R22" t="n">
-        <v>7208532</v>
+        <v>7208531</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3047,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188865</v>
+        <v>113188893</v>
       </c>
       <c r="B23" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,39 +3068,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544430</v>
+        <v>544429</v>
       </c>
       <c r="R23" t="n">
-        <v>7208372</v>
+        <v>7208373</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188876</v>
+        <v>113188882</v>
       </c>
       <c r="B24" t="n">
-        <v>90053</v>
+        <v>78155</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,21 +3180,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544013</v>
+        <v>543905</v>
       </c>
       <c r="R24" t="n">
-        <v>7208531</v>
+        <v>7208555</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188880</v>
+        <v>113188857</v>
       </c>
       <c r="B25" t="n">
-        <v>78133</v>
+        <v>74336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,21 +3292,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543869</v>
+        <v>544013</v>
       </c>
       <c r="R25" t="n">
-        <v>7208524</v>
+        <v>7208532</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188881</v>
+        <v>113188883</v>
       </c>
       <c r="B26" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543877</v>
+        <v>543970</v>
       </c>
       <c r="R26" t="n">
-        <v>7208540</v>
+        <v>7208506</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,10 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113188895</v>
+        <v>113188873</v>
       </c>
       <c r="B27" t="n">
-        <v>78133</v>
+        <v>77512</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3512,25 +3512,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544444</v>
+        <v>544156</v>
       </c>
       <c r="R27" t="n">
-        <v>7208349</v>
+        <v>7208494</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,10 +3612,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113188857</v>
+        <v>113188879</v>
       </c>
       <c r="B28" t="n">
-        <v>74314</v>
+        <v>90097</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3628,21 +3628,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544013</v>
+        <v>544428</v>
       </c>
       <c r="R28" t="n">
-        <v>7208532</v>
+        <v>7208357</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3724,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113188884</v>
+        <v>113188889</v>
       </c>
       <c r="B29" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544013</v>
+        <v>544243</v>
       </c>
       <c r="R29" t="n">
-        <v>7208532</v>
+        <v>7208437</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,10 +3836,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113188894</v>
+        <v>113188895</v>
       </c>
       <c r="B30" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544427</v>
+        <v>544444</v>
       </c>
       <c r="R30" t="n">
-        <v>7208357</v>
+        <v>7208349</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113188859</v>
+        <v>113188872</v>
       </c>
       <c r="B31" t="n">
-        <v>90057</v>
+        <v>77136</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543970</v>
+        <v>544389</v>
       </c>
       <c r="R31" t="n">
-        <v>7208507</v>
+        <v>7208365</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113188879</v>
+        <v>113188884</v>
       </c>
       <c r="B32" t="n">
-        <v>90075</v>
+        <v>78155</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544428</v>
+        <v>544013</v>
       </c>
       <c r="R32" t="n">
-        <v>7208357</v>
+        <v>7208532</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,7 +4172,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113188860</v>
+        <v>113188865</v>
       </c>
       <c r="B33" t="n">
         <v>56766</v>
@@ -4208,7 +4208,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543868</v>
+        <v>544430</v>
       </c>
       <c r="R33" t="n">
-        <v>7208522</v>
+        <v>7208372</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -2940,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188876</v>
+        <v>113188893</v>
       </c>
       <c r="B22" t="n">
-        <v>90075</v>
+        <v>78155</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,21 +2956,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544013</v>
+        <v>544429</v>
       </c>
       <c r="R22" t="n">
-        <v>7208531</v>
+        <v>7208373</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188893</v>
+        <v>113188876</v>
       </c>
       <c r="B23" t="n">
-        <v>78155</v>
+        <v>90075</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,21 +3068,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544429</v>
+        <v>544013</v>
       </c>
       <c r="R23" t="n">
-        <v>7208373</v>
+        <v>7208531</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188880</v>
+        <v>113188886</v>
       </c>
       <c r="B2" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543869</v>
+        <v>544163</v>
       </c>
       <c r="R2" t="n">
-        <v>7208524</v>
+        <v>7208441</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188898</v>
+        <v>113188876</v>
       </c>
       <c r="B3" t="n">
-        <v>81896</v>
+        <v>90079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,7 +830,7 @@
         <v>544013</v>
       </c>
       <c r="R3" t="n">
-        <v>7208532</v>
+        <v>7208531</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188860</v>
+        <v>113188883</v>
       </c>
       <c r="B4" t="n">
-        <v>56766</v>
+        <v>78158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543868</v>
+        <v>543970</v>
       </c>
       <c r="R4" t="n">
-        <v>7208522</v>
+        <v>7208506</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188891</v>
+        <v>113188898</v>
       </c>
       <c r="B5" t="n">
-        <v>78155</v>
+        <v>81900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544389</v>
+        <v>544013</v>
       </c>
       <c r="R5" t="n">
-        <v>7208365</v>
+        <v>7208532</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188878</v>
+        <v>113188888</v>
       </c>
       <c r="B6" t="n">
-        <v>90097</v>
+        <v>78158</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,7 +1163,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544229</v>
+        <v>544228</v>
       </c>
       <c r="R6" t="n">
         <v>7208430</v>
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188890</v>
+        <v>113188892</v>
       </c>
       <c r="B7" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544344</v>
+        <v>544425</v>
       </c>
       <c r="R7" t="n">
-        <v>7208412</v>
+        <v>7208367</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188881</v>
+        <v>113188859</v>
       </c>
       <c r="B8" t="n">
-        <v>78155</v>
+        <v>90083</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543877</v>
+        <v>543970</v>
       </c>
       <c r="R8" t="n">
-        <v>7208540</v>
+        <v>7208507</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188892</v>
+        <v>113188891</v>
       </c>
       <c r="B9" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544425</v>
+        <v>544389</v>
       </c>
       <c r="R9" t="n">
-        <v>7208367</v>
+        <v>7208365</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188864</v>
+        <v>113188873</v>
       </c>
       <c r="B10" t="n">
-        <v>56766</v>
+        <v>77515</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,43 +1583,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544419</v>
+        <v>544156</v>
       </c>
       <c r="R10" t="n">
-        <v>7208372</v>
+        <v>7208494</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188886</v>
+        <v>113188880</v>
       </c>
       <c r="B11" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544163</v>
+        <v>543869</v>
       </c>
       <c r="R11" t="n">
-        <v>7208441</v>
+        <v>7208524</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188877</v>
+        <v>113188885</v>
       </c>
       <c r="B12" t="n">
-        <v>90097</v>
+        <v>78158</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543877</v>
+        <v>544156</v>
       </c>
       <c r="R12" t="n">
-        <v>7208540</v>
+        <v>7208494</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188869</v>
+        <v>113188877</v>
       </c>
       <c r="B13" t="n">
-        <v>74341</v>
+        <v>90101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544425</v>
+        <v>543877</v>
       </c>
       <c r="R13" t="n">
-        <v>7208380</v>
+        <v>7208540</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188885</v>
+        <v>113188895</v>
       </c>
       <c r="B14" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544156</v>
+        <v>544444</v>
       </c>
       <c r="R14" t="n">
-        <v>7208494</v>
+        <v>7208349</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188888</v>
+        <v>113188857</v>
       </c>
       <c r="B15" t="n">
-        <v>78155</v>
+        <v>74339</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544228</v>
+        <v>544013</v>
       </c>
       <c r="R15" t="n">
-        <v>7208430</v>
+        <v>7208532</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188894</v>
+        <v>113188858</v>
       </c>
       <c r="B16" t="n">
-        <v>78155</v>
+        <v>74339</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544427</v>
+        <v>544389</v>
       </c>
       <c r="R16" t="n">
-        <v>7208357</v>
+        <v>7208368</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188858</v>
+        <v>113188878</v>
       </c>
       <c r="B17" t="n">
-        <v>74336</v>
+        <v>90101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544389</v>
+        <v>544229</v>
       </c>
       <c r="R17" t="n">
-        <v>7208368</v>
+        <v>7208430</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188859</v>
+        <v>113188860</v>
       </c>
       <c r="B18" t="n">
-        <v>90079</v>
+        <v>56769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,34 +2483,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543970</v>
+        <v>543868</v>
       </c>
       <c r="R18" t="n">
-        <v>7208507</v>
+        <v>7208522</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188861</v>
+        <v>113188863</v>
       </c>
       <c r="B19" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544162</v>
+        <v>544344</v>
       </c>
       <c r="R19" t="n">
-        <v>7208445</v>
+        <v>7208412</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,12 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188875</v>
+        <v>113188884</v>
       </c>
       <c r="B20" t="n">
-        <v>78236</v>
+        <v>78158</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2823,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188863</v>
+        <v>113188869</v>
       </c>
       <c r="B21" t="n">
-        <v>56766</v>
+        <v>74344</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,39 +2829,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544344</v>
+        <v>544425</v>
       </c>
       <c r="R21" t="n">
-        <v>7208412</v>
+        <v>7208380</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2903,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188893</v>
+        <v>113188890</v>
       </c>
       <c r="B22" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2980,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544429</v>
+        <v>544344</v>
       </c>
       <c r="R22" t="n">
-        <v>7208373</v>
+        <v>7208412</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3015,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188876</v>
+        <v>113188881</v>
       </c>
       <c r="B23" t="n">
-        <v>90075</v>
+        <v>78158</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,21 +3053,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3092,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544013</v>
+        <v>543877</v>
       </c>
       <c r="R23" t="n">
-        <v>7208531</v>
+        <v>7208540</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188882</v>
+        <v>113188894</v>
       </c>
       <c r="B24" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543905</v>
+        <v>544427</v>
       </c>
       <c r="R24" t="n">
-        <v>7208555</v>
+        <v>7208357</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188857</v>
+        <v>113188879</v>
       </c>
       <c r="B25" t="n">
-        <v>74336</v>
+        <v>90101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,21 +3277,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3316,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544013</v>
+        <v>544428</v>
       </c>
       <c r="R25" t="n">
-        <v>7208532</v>
+        <v>7208357</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3351,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188883</v>
+        <v>113188882</v>
       </c>
       <c r="B26" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3428,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543970</v>
+        <v>543905</v>
       </c>
       <c r="R26" t="n">
-        <v>7208506</v>
+        <v>7208555</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3463,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113188873</v>
+        <v>113188889</v>
       </c>
       <c r="B27" t="n">
-        <v>77512</v>
+        <v>78158</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3512,25 +3497,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3540,10 +3525,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544156</v>
+        <v>544243</v>
       </c>
       <c r="R27" t="n">
-        <v>7208494</v>
+        <v>7208437</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3575,7 +3560,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3585,7 +3570,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,10 +3597,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113188879</v>
+        <v>113188864</v>
       </c>
       <c r="B28" t="n">
-        <v>90097</v>
+        <v>56769</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3628,34 +3613,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544428</v>
+        <v>544419</v>
       </c>
       <c r="R28" t="n">
-        <v>7208357</v>
+        <v>7208372</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3687,7 +3677,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,7 +3687,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3724,10 +3714,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113188889</v>
+        <v>113188893</v>
       </c>
       <c r="B29" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,10 +3754,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544243</v>
+        <v>544429</v>
       </c>
       <c r="R29" t="n">
-        <v>7208437</v>
+        <v>7208373</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3799,7 +3789,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3799,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,10 +3826,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113188895</v>
+        <v>113188872</v>
       </c>
       <c r="B30" t="n">
-        <v>78155</v>
+        <v>77139</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3852,21 +3842,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3876,10 +3866,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544444</v>
+        <v>544389</v>
       </c>
       <c r="R30" t="n">
-        <v>7208349</v>
+        <v>7208365</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3911,7 +3901,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3911,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,10 +3938,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113188872</v>
+        <v>113188865</v>
       </c>
       <c r="B31" t="n">
-        <v>77136</v>
+        <v>56769</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,34 +3954,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544389</v>
+        <v>544430</v>
       </c>
       <c r="R31" t="n">
-        <v>7208365</v>
+        <v>7208372</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4023,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113188884</v>
+        <v>113188861</v>
       </c>
       <c r="B32" t="n">
-        <v>78155</v>
+        <v>56769</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,34 +4071,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544013</v>
+        <v>544162</v>
       </c>
       <c r="R32" t="n">
-        <v>7208532</v>
+        <v>7208445</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +4145,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113188865</v>
+        <v>113188875</v>
       </c>
       <c r="B33" t="n">
-        <v>56766</v>
+        <v>78240</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4188,39 +4193,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544430</v>
+        <v>544013</v>
       </c>
       <c r="R33" t="n">
-        <v>7208372</v>
+        <v>7208532</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188886</v>
+        <v>113188876</v>
       </c>
       <c r="B2" t="n">
-        <v>78158</v>
+        <v>90079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544163</v>
+        <v>544013</v>
       </c>
       <c r="R2" t="n">
-        <v>7208441</v>
+        <v>7208531</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188876</v>
+        <v>113188886</v>
       </c>
       <c r="B3" t="n">
-        <v>90079</v>
+        <v>78158</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544013</v>
+        <v>544163</v>
       </c>
       <c r="R3" t="n">
-        <v>7208531</v>
+        <v>7208441</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188878</v>
+        <v>113188860</v>
       </c>
       <c r="B17" t="n">
-        <v>90101</v>
+        <v>56769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,34 +2371,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544229</v>
+        <v>543868</v>
       </c>
       <c r="R17" t="n">
-        <v>7208430</v>
+        <v>7208522</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,7 +2472,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188860</v>
+        <v>113188863</v>
       </c>
       <c r="B18" t="n">
         <v>56769</v>
@@ -2503,7 +2508,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2512,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543868</v>
+        <v>544344</v>
       </c>
       <c r="R18" t="n">
-        <v>7208522</v>
+        <v>7208412</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188863</v>
+        <v>113188878</v>
       </c>
       <c r="B19" t="n">
-        <v>56769</v>
+        <v>90101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,39 +2605,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544344</v>
+        <v>544229</v>
       </c>
       <c r="R19" t="n">
-        <v>7208412</v>
+        <v>7208430</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188876</v>
+        <v>113188861</v>
       </c>
       <c r="B2" t="n">
-        <v>90079</v>
+        <v>56773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544013</v>
+        <v>544162</v>
       </c>
       <c r="R2" t="n">
-        <v>7208531</v>
+        <v>7208445</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188886</v>
+        <v>113188893</v>
       </c>
       <c r="B3" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544163</v>
+        <v>544429</v>
       </c>
       <c r="R3" t="n">
-        <v>7208441</v>
+        <v>7208373</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188883</v>
+        <v>113188894</v>
       </c>
       <c r="B4" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543970</v>
+        <v>544427</v>
       </c>
       <c r="R4" t="n">
-        <v>7208506</v>
+        <v>7208357</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188898</v>
+        <v>113188880</v>
       </c>
       <c r="B5" t="n">
-        <v>81900</v>
+        <v>78164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544013</v>
+        <v>543869</v>
       </c>
       <c r="R5" t="n">
-        <v>7208532</v>
+        <v>7208524</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188888</v>
+        <v>113188881</v>
       </c>
       <c r="B6" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544228</v>
+        <v>543877</v>
       </c>
       <c r="R6" t="n">
-        <v>7208430</v>
+        <v>7208540</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,7 +1248,7 @@
         <v>113188892</v>
       </c>
       <c r="B7" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188859</v>
+        <v>113188864</v>
       </c>
       <c r="B8" t="n">
-        <v>90083</v>
+        <v>56773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,34 +1373,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543970</v>
+        <v>544419</v>
       </c>
       <c r="R8" t="n">
-        <v>7208507</v>
+        <v>7208372</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188891</v>
+        <v>113188898</v>
       </c>
       <c r="B9" t="n">
-        <v>78158</v>
+        <v>81906</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544389</v>
+        <v>544013</v>
       </c>
       <c r="R9" t="n">
-        <v>7208365</v>
+        <v>7208532</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188873</v>
+        <v>113188876</v>
       </c>
       <c r="B10" t="n">
-        <v>77515</v>
+        <v>90085</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1598,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>498</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544156</v>
+        <v>544013</v>
       </c>
       <c r="R10" t="n">
-        <v>7208494</v>
+        <v>7208531</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188880</v>
+        <v>113188865</v>
       </c>
       <c r="B11" t="n">
-        <v>78158</v>
+        <v>56773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,34 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543869</v>
+        <v>544430</v>
       </c>
       <c r="R11" t="n">
-        <v>7208524</v>
+        <v>7208372</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188885</v>
+        <v>113188886</v>
       </c>
       <c r="B12" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544156</v>
+        <v>544163</v>
       </c>
       <c r="R12" t="n">
-        <v>7208494</v>
+        <v>7208441</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188877</v>
+        <v>113188889</v>
       </c>
       <c r="B13" t="n">
-        <v>90101</v>
+        <v>78164</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1943,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543877</v>
+        <v>544243</v>
       </c>
       <c r="R13" t="n">
-        <v>7208540</v>
+        <v>7208437</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188895</v>
+        <v>113188857</v>
       </c>
       <c r="B14" t="n">
-        <v>78158</v>
+        <v>74345</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2055,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544444</v>
+        <v>544013</v>
       </c>
       <c r="R14" t="n">
-        <v>7208349</v>
+        <v>7208532</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188857</v>
+        <v>113188878</v>
       </c>
       <c r="B15" t="n">
-        <v>74339</v>
+        <v>90107</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2167,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544013</v>
+        <v>544229</v>
       </c>
       <c r="R15" t="n">
-        <v>7208532</v>
+        <v>7208430</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,7 +2266,7 @@
         <v>113188858</v>
       </c>
       <c r="B16" t="n">
-        <v>74339</v>
+        <v>74345</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2355,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188860</v>
+        <v>113188859</v>
       </c>
       <c r="B17" t="n">
-        <v>56769</v>
+        <v>90089</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,39 +2391,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543868</v>
+        <v>543970</v>
       </c>
       <c r="R17" t="n">
-        <v>7208522</v>
+        <v>7208507</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188863</v>
+        <v>113188860</v>
       </c>
       <c r="B18" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,7 +2523,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2517,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544344</v>
+        <v>543868</v>
       </c>
       <c r="R18" t="n">
-        <v>7208412</v>
+        <v>7208522</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188878</v>
+        <v>113188891</v>
       </c>
       <c r="B19" t="n">
-        <v>90101</v>
+        <v>78164</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,21 +2620,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544229</v>
+        <v>544389</v>
       </c>
       <c r="R19" t="n">
-        <v>7208430</v>
+        <v>7208365</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188884</v>
+        <v>113188873</v>
       </c>
       <c r="B20" t="n">
-        <v>78158</v>
+        <v>77521</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2713,25 +2728,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544013</v>
+        <v>544156</v>
       </c>
       <c r="R20" t="n">
-        <v>7208532</v>
+        <v>7208494</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188869</v>
+        <v>113188875</v>
       </c>
       <c r="B21" t="n">
-        <v>74344</v>
+        <v>78246</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,21 +2844,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544425</v>
+        <v>544013</v>
       </c>
       <c r="R21" t="n">
-        <v>7208380</v>
+        <v>7208532</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188890</v>
+        <v>113188884</v>
       </c>
       <c r="B22" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2965,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544344</v>
+        <v>544013</v>
       </c>
       <c r="R22" t="n">
-        <v>7208412</v>
+        <v>7208532</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188881</v>
+        <v>113188879</v>
       </c>
       <c r="B23" t="n">
-        <v>78158</v>
+        <v>90107</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,21 +3068,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543877</v>
+        <v>544428</v>
       </c>
       <c r="R23" t="n">
-        <v>7208540</v>
+        <v>7208357</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188894</v>
+        <v>113188895</v>
       </c>
       <c r="B24" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3189,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544427</v>
+        <v>544444</v>
       </c>
       <c r="R24" t="n">
-        <v>7208357</v>
+        <v>7208349</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3224,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188879</v>
+        <v>113188888</v>
       </c>
       <c r="B25" t="n">
-        <v>90101</v>
+        <v>78164</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,21 +3292,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544428</v>
+        <v>544228</v>
       </c>
       <c r="R25" t="n">
-        <v>7208357</v>
+        <v>7208430</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188882</v>
+        <v>113188885</v>
       </c>
       <c r="B26" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3413,10 +3428,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543905</v>
+        <v>544156</v>
       </c>
       <c r="R26" t="n">
-        <v>7208555</v>
+        <v>7208494</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,10 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113188889</v>
+        <v>113188872</v>
       </c>
       <c r="B27" t="n">
-        <v>78158</v>
+        <v>77145</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,21 +3516,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3525,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544243</v>
+        <v>544389</v>
       </c>
       <c r="R27" t="n">
-        <v>7208437</v>
+        <v>7208365</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3560,7 +3575,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3585,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,10 +3612,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113188864</v>
+        <v>113188877</v>
       </c>
       <c r="B28" t="n">
-        <v>56769</v>
+        <v>90107</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3613,39 +3628,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544419</v>
+        <v>543877</v>
       </c>
       <c r="R28" t="n">
-        <v>7208372</v>
+        <v>7208540</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3677,7 +3687,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3697,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113188893</v>
+        <v>113188882</v>
       </c>
       <c r="B29" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3754,10 +3764,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544429</v>
+        <v>543905</v>
       </c>
       <c r="R29" t="n">
-        <v>7208373</v>
+        <v>7208555</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3789,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3826,10 +3836,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113188872</v>
+        <v>113188883</v>
       </c>
       <c r="B30" t="n">
-        <v>77139</v>
+        <v>78164</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3842,21 +3852,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3866,10 +3876,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544389</v>
+        <v>543970</v>
       </c>
       <c r="R30" t="n">
-        <v>7208365</v>
+        <v>7208506</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3901,7 +3911,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,7 +3921,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113188865</v>
+        <v>113188890</v>
       </c>
       <c r="B31" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3954,39 +3964,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544430</v>
+        <v>544344</v>
       </c>
       <c r="R31" t="n">
-        <v>7208372</v>
+        <v>7208412</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4028,7 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4055,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113188861</v>
+        <v>113188869</v>
       </c>
       <c r="B32" t="n">
-        <v>56769</v>
+        <v>74350</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4071,39 +4076,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544162</v>
+        <v>544425</v>
       </c>
       <c r="R32" t="n">
-        <v>7208445</v>
+        <v>7208380</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,12 +4145,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,10 +4172,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113188875</v>
+        <v>113188863</v>
       </c>
       <c r="B33" t="n">
-        <v>78240</v>
+        <v>56773</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4193,34 +4188,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544013</v>
+        <v>544344</v>
       </c>
       <c r="R33" t="n">
-        <v>7208532</v>
+        <v>7208412</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 48247-2023 artfynd.xlsx
+++ b/artfynd/A 48247-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
